--- a/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.2.0</t>
+    <t>2026.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:53:17+00:00</t>
+    <t>2026-06-14T20:00:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>14</t>
+    <t>17</t>
   </si>
   <si>
     <t>Level</t>
@@ -159,6 +159,12 @@
     <t>PROMIS-29 Questionnaire</t>
   </si>
   <si>
+    <t>promis-promis16</t>
+  </si>
+  <si>
+    <t>PROMIS-16 Profile Questionnaire (ultra-short 8-domain profile)</t>
+  </si>
+  <si>
     <t>promis-depression-sf4a</t>
   </si>
   <si>
@@ -217,6 +223,18 @@
   </si>
   <si>
     <t>PRO-CTCAE German Breast Cancer Subset (21 Symptoms)</t>
+  </si>
+  <si>
+    <t>proctcae-onkologisches-basisscreening</t>
+  </si>
+  <si>
+    <t>PRO-CTCAE Onkologisches Basisscreening (DKG, MIDOS2-äquivalente Symptome)</t>
+  </si>
+  <si>
+    <t>midos-midos2</t>
+  </si>
+  <si>
+    <t>MIDOS2 (Minimales Dokumentationssystem für Palliativpatienten, DGP)</t>
   </si>
 </sst>
 </file>
@@ -522,7 +540,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -707,6 +725,42 @@
       </c>
       <c r="D15" s="2"/>
     </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D18" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.4.0</t>
+    <t>2026.4.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-14T20:00:22+00:00</t>
+    <t>2026-06-15T12:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:52:47+00:00</t>
+    <t>2026-07-07T06:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>17</t>
+    <t>18</t>
   </si>
   <si>
     <t>Level</t>
@@ -145,6 +145,12 @@
   </si>
   <si>
     <t>PHQ-9 Questionnaire</t>
+  </si>
+  <si>
+    <t>phq-phq15</t>
+  </si>
+  <si>
+    <t>PHQ-15 Questionnaire</t>
   </si>
   <si>
     <t>bdi-bdi2</t>
@@ -540,7 +546,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -761,6 +767,18 @@
       </c>
       <c r="D18" s="2"/>
     </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="D19" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="78">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.4.1</t>
+    <t>2026.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T06:23:56+00:00</t>
+    <t>2026-07-07T13:30:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>18</t>
+    <t>19</t>
   </si>
   <si>
     <t>Level</t>
@@ -241,6 +241,12 @@
   </si>
   <si>
     <t>MIDOS2 (Minimales Dokumentationssystem für Palliativpatienten, DGP)</t>
+  </si>
+  <si>
+    <t>whodas-whodas12</t>
+  </si>
+  <si>
+    <t>WHODAS 2.0 12-Item (WHO Disability Assessment Schedule 2.0, self-administered)</t>
   </si>
 </sst>
 </file>
@@ -546,7 +552,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -779,6 +785,18 @@
       </c>
       <c r="D19" s="2"/>
     </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D20" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T13:30:17+00:00</t>
+    <t>2026-07-07T13:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T13:37:50+00:00</t>
+    <t>2026-07-07T13:59:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.5.0</t>
+    <t>2026.5.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T13:59:08+00:00</t>
+    <t>2026-07-27T21:31:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="90">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.5.2</t>
+    <t>2026.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T21:31:58+00:00</t>
+    <t>2026-09-02T06:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>19</t>
+    <t>25</t>
   </si>
   <si>
     <t>Level</t>
@@ -247,6 +247,42 @@
   </si>
   <si>
     <t>WHODAS 2.0 12-Item (WHO Disability Assessment Schedule 2.0, self-administered)</t>
+  </si>
+  <si>
+    <t>scoff</t>
+  </si>
+  <si>
+    <t>SCOFF (Five-item eating disorder screening questionnaire, Morgan et al. 1999)</t>
+  </si>
+  <si>
+    <t>wi-7</t>
+  </si>
+  <si>
+    <t>Whiteley-7 (Seven-item scale for hypochondriasis and somatization, Fink et al. 1999)</t>
+  </si>
+  <si>
+    <t>pc-ptsd</t>
+  </si>
+  <si>
+    <t>PC-PTSD (Primary Care PTSD Screen)</t>
+  </si>
+  <si>
+    <t>ssd-12</t>
+  </si>
+  <si>
+    <t>SSD-12 (Somatic Symptom Disorder - B Criteria Scale, Toussaint et al.)</t>
+  </si>
+  <si>
+    <t>isr-z</t>
+  </si>
+  <si>
+    <t>ISR-Z (ICD-10-Symptom-Rating, Subskala Zwang, Tritt et al. 2008)</t>
+  </si>
+  <si>
+    <t>euronet-soma</t>
+  </si>
+  <si>
+    <t>EURONET-SOMA (Core outcome single items for somatic symptom burden, Rief et al. 2017)</t>
   </si>
 </sst>
 </file>
@@ -552,7 +588,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -797,6 +833,78 @@
       </c>
       <c r="D20" s="2"/>
     </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="D26" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.6.0</t>
+    <t>2026.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:53+00:00</t>
+    <t>2026-09-02T06:41:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>25</t>
+    <t>26</t>
   </si>
   <si>
     <t>Level</t>
@@ -283,6 +283,12 @@
   </si>
   <si>
     <t>EURONET-SOMA (Core outcome single items for somatic symptom burden, Rief et al. 2017)</t>
+  </si>
+  <si>
+    <t>phq-gad7</t>
+  </si>
+  <si>
+    <t>GAD-7 (Generalized Anxiety Disorder Scale-7, Spitzer et al. 2006)</t>
   </si>
 </sst>
 </file>
@@ -588,7 +594,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -905,6 +911,18 @@
       </c>
       <c r="D26" s="2"/>
     </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="D27" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:55+00:00</t>
+    <t>2026-09-02T06:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-questionnaire-catalogue.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:47:03+00:00</t>
+    <t>2026-09-02T07:20:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
